--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/SOUTH_CAROLINA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/SOUTH_CAROLINA_2010.xlsx
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C133">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C144">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C543">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C585">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C600">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C968">
